--- a/engine/publish_queue/PHAR/EIPICO_Valuation_Model_10092026.xlsx
+++ b/engine/publish_queue/PHAR/EIPICO_Valuation_Model_10092026.xlsx
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>103.8007679145783</v>
+        <v>104.9105272908218</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>94.39540498598306</v>
+        <v>96.08964646722389</v>
       </c>
     </row>
     <row r="6">
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>120.563279729777</v>
+        <v>121.951229622625</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>118.416837770352</v>
+        <v>120.5086214711495</v>
       </c>
     </row>
     <row r="7">
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>131.6933256819726</v>
+        <v>132.7208728267296</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>135.3037034307837</v>
+        <v>136.8658343216828</v>
       </c>
     </row>
     <row r="8">
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>143.9429398845258</v>
+        <v>144.4479983997303</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>154.3933534707429</v>
+        <v>155.4373533791256</v>
       </c>
     </row>
     <row r="9">
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>167.1694824698633</v>
+        <v>167.8488827718508</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>193.8196590270854</v>
+        <v>194.5986082406631</v>
       </c>
     </row>
     <row r="10">
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>0.5380200000000001</v>
+        <v>0.56606</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>0.58168</v>
+        <v>0.60784</v>
       </c>
     </row>
     <row r="11">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="B11" s="17" t="n">
-        <v>0.26388</v>
+        <v>0.27418</v>
       </c>
       <c r="C11" s="17" t="n">
-        <v>0.38614</v>
+        <v>0.40504</v>
       </c>
     </row>
     <row r="12">
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="B12" s="17" t="n">
-        <v>0.1869</v>
+        <v>0.16364</v>
       </c>
       <c r="C12" s="17" t="n">
-        <v>0.23222</v>
+        <v>0.20604</v>
       </c>
     </row>
     <row r="13">
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>0.43044</v>
+        <v>0.43642</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>0.63828</v>
+        <v>0.64934</v>
       </c>
     </row>
     <row r="14">
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>0.3294</v>
+        <v>0.29892</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>0.47868</v>
+        <v>0.4396</v>
       </c>
     </row>
     <row r="15">
